--- a/stories/arbres/TREE-SAN-010.xlsx
+++ b/stories/arbres/TREE-SAN-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Zoé est dans la cuisine. Papa cuisine. Maman dresse la table. Il y a des copains. Dans la poêle, des légumes. Papa dit : on peut goûter une petite portion. Puis nommer le goût.</t>
+          <t>Le soir, Zoé est dans la cuisine. Papa cuisine. Maman dresse la table. Il y a des copains. Dans la poêle, des légumes. On peut goûter une petite portion. Puis nommer le goût.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Zoé est dans la cuisine. Papa cuisine. Maman dresse la table. Il y a des copains. Dans la poêle, des légumes.
+papa|On peut goûter une petite portion.
+narrateur|Puis nommer le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1517,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1657,6 +1686,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit près de Zoé. Papa sert des brocolis. Zoé goûte une petite portion. C'est un peu croquant. Elle nomme le goût : c'est doux, papa. Tom écoute.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1867,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé goûte le brocoli. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2040,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Tom applaudit.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2235,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2215,7 +2264,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Zoé et Tom empilent des cubes. Zoé dit : j'ai goûté une petite portion. J'ai nommé le goût. Tom pose un cube vert, comme le brocoli.</t>
+          <t>Zoé et Tom empilent des cubes. J'ai goûté une petite portion. J'ai nommé le goût. Tom pose un cube vert, comme le brocoli.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2353,6 +2402,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé et Tom empilent des cubes.
+enfant-f|J'ai goûté une petite portion. J'ai nommé le goût. Tom pose un cube vert, comme le brocoli.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2598,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2567,7 +2627,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : c'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Tom sourit.</t>
+          <t>C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Tom sourit.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2705,6 +2765,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>enfant-f|C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2932,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2891,7 +2961,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Tom hoche.</t>
+          <t>Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Tom hoche.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3029,6 +3099,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Tom hoche.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3266,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3215,7 +3295,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : c'est croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>C'est croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3353,6 +3433,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>enfant-f|C'est croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3600,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3767,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maman ouvre un livre de légumes. Zoé montre le brocoli. Elle a goûté une petite portion. Elle nomme le goût. Tom tourne la page.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3962,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3891,7 +3991,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Dans le livre, Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Dans le livre, Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4029,6 +4129,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le livre,
+enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4297,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4215,7 +4326,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé, un peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Salé, un peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4353,6 +4464,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé, un peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4631,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4539,7 +4660,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom rit.</t>
+          <t>Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom rit.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4677,6 +4798,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>enfant-f|Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom rit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4965,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5132,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Ils font la dînette. Zoé sert un tout petit brocoli. Elle a goûté une petite portion, pour de vrai. Elle nomme le goût. Tom sert de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5327,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5215,7 +5356,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>À la dînette, Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>À la dînette, Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5353,6 +5494,12 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|À la dînette,
+enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5662,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5539,7 +5691,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5677,6 +5829,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5996,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5863,7 +6025,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom tapote.</t>
+          <t>Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom tapote.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6001,6 +6163,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>enfant-f|Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom tapote.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6330,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6325,6 +6497,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a une assiette de betterave. Elle est rose. Zoé goûte une petite portion. C'est terreux et doux. Elle nomme le goût : c'est doux, maman. Léa ouvre les yeux.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6678,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé goûte la betterave. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6851,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Les lèvres de Zoé sont un peu roses. Elle a goûté. Elle a nommé le goût. Une petite portion.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6859,6 +7046,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6883,7 +7075,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa choisit un cube rose. Zoé aussi. Zoé dit : j'ai goûté une petite portion. J'ai nommé le goût.</t>
+          <t>Léa choisit un cube rose. Zoé aussi. J'ai goûté une petite portion. J'ai nommé le goût.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7021,6 +7213,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa choisit un cube rose. Zoé aussi.
+enfant-f|J'ai goûté une petite portion. J'ai nommé le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7211,6 +7409,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7235,7 +7438,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux et rose. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Doux et rose. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7373,6 +7576,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux et rose. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7535,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7559,7 +7772,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : un peu salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Un peu salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7697,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7859,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7883,7 +8106,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : pas trop croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Pas trop croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8021,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>enfant-f|Pas trop croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8183,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8345,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le livre, une betterave. Léa montre. Zoé a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8535,6 +8773,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8559,7 +8802,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit.</t>
+          <t>Doux. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8697,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8859,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8883,7 +9136,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé. Elle a goûté une petite portion. Elle nomme le goût. Papa sourit.</t>
+          <t>Salé. Elle a goûté une petite portion. Elle nomme le goût. Papa sourit.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9021,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9183,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9207,7 +9470,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : tendre, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Tendre, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9345,6 +9608,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>enfant-f|Tendre, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9507,6 +9775,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9669,6 +9942,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|À la dînette, Léa sert du rose. Zoé a goûté une petite portion pour de vrai. Elle nomme le goût. Maman rit.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9859,6 +10137,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9883,7 +10166,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10021,6 +10304,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10183,6 +10471,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10207,7 +10500,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé, un tout petit peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Salé, un tout petit peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10345,6 +10638,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé, un tout petit peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10507,6 +10805,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10531,7 +10834,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10669,6 +10972,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>enfant-f|Mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10831,6 +11139,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10993,6 +11306,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a des épinards. Ils sont verts et chauds. Zoé goûte une petite portion. C'est fondant. Elle nomme le goût : c'est doux, papa. Sami hoche.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11487,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé goûte les épinards. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11660,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a goûté les épinards. Elle a nommé le goût. Une petite portion.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11527,6 +11855,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11551,7 +11884,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami bâtit une tour verte. Zoé dit : j'ai goûté une petite portion. J'ai nommé le goût.</t>
+          <t>Sami bâtit une tour verte. J'ai goûté une petite portion. J'ai nommé le goût.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11689,6 +12022,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami bâtit une tour verte.
+enfant-f|J'ai goûté une petite portion. J'ai nommé le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11879,6 +12218,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11903,7 +12247,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût. Sami pose un cube.</t>
+          <t>Doux. Elle a goûté une petite portion. Elle nomme le goût. Sami pose un cube.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12041,6 +12385,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût. Sami pose un cube.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12203,6 +12552,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12227,7 +12581,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Maman range.</t>
+          <t>Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Maman range.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12365,6 +12719,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Maman range.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12527,6 +12886,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12551,7 +12915,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : fondant, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Fondant, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12689,6 +13053,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>enfant-f|Fondant, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12851,6 +13220,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13013,6 +13387,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami trouve les épinards dans le livre. Zoé a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13203,6 +13582,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13227,7 +13611,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût. Ils se taisent une seconde.</t>
+          <t>Doux. Elle a goûté une petite portion. Elle nomme le goût. Ils se taisent une seconde.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13365,6 +13749,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.
+narrateur|Ils se taisent une seconde.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13527,6 +13917,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13551,7 +13946,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé. Elle a goûté une petite portion. Elle nomme le goût. Sami ferme le livre.</t>
+          <t>Salé. Elle a goûté une petite portion. Elle nomme le goût. Sami ferme le livre.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13689,6 +14084,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût. Sami ferme le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13851,6 +14251,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13875,7 +14280,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14013,6 +14418,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>enfant-f|Pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14175,6 +14585,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14199,7 +14614,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>À la dînette, Sami sert du vert. Zoé a goûté une petite portion. Elle nomme le goût. Papa dit : merci d'avoir dit le goût.</t>
+          <t>À la dînette, Sami sert du vert. Zoé a goûté une petite portion. Elle nomme le goût. Merci d'avoir dit le goût.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14337,6 +14752,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|À la dînette, Sami sert du vert. Zoé a goûté une petite portion. Elle nomme le goût.
+papa|Merci d'avoir dit le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14527,6 +14948,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14551,7 +14977,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : doux. Elle a goûté une petite portion. Elle nomme le goût. Un oiseau chante.</t>
+          <t>Doux. Elle a goûté une petite portion. Elle nomme le goût. Un oiseau chante.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14689,6 +15115,12 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.
+narrateur|Un oiseau chante.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14851,6 +15283,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14875,7 +15312,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : salé. Elle a goûté une petite portion. Elle nomme le goût. La lumière est douce.</t>
+          <t>Salé. Elle a goûté une petite portion. Elle nomme le goût. La lumière est douce.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15013,6 +15450,12 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût.
+narrateur|La lumière est douce.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15175,6 +15618,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15199,7 +15647,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit : tout mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+          <t>Tout mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15337,6 +15785,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>enfant-f|Tout mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15499,6 +15952,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15517,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15534,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-010.xlsx
+++ b/stories/arbres/TREE-SAN-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis nommer le goût.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1524,6 +1530,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1691,6 +1698,7 @@
           <t>narrateur|Tom s'assoit près de Zoé. Papa sert des brocolis. Zoé goûte une petite portion. C'est un peu croquant. Elle nomme le goût : c'est doux, papa. Tom écoute.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1874,6 +1882,7 @@
           <t>narrateur|Zoé goûte le brocoli. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2045,6 +2054,7 @@
           <t>narrateur|Zoé a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Tom applaudit.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2240,6 +2250,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2408,6 +2419,7 @@
 enfant-f|J'ai goûté une petite portion. J'ai nommé le goût. Tom pose un cube vert, comme le brocoli.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2603,6 +2615,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2770,6 +2783,7 @@
           <t>enfant-f|C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2937,6 +2951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3104,6 +3119,7 @@
           <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Tom hoche.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3271,6 +3287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3438,6 +3455,7 @@
           <t>enfant-f|C'est croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3605,6 +3623,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3772,6 +3791,7 @@
           <t>narrateur|Maman ouvre un livre de légumes. Zoé montre le brocoli. Elle a goûté une petite portion. Elle nomme le goût. Tom tourne la page.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3967,6 +3987,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4135,6 +4156,7 @@
 enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4302,6 +4324,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4469,6 +4492,7 @@
           <t>enfant-f|Salé, un peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4636,6 +4660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4803,6 +4828,7 @@
           <t>enfant-f|Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom rit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4970,6 +4996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5137,6 +5164,7 @@
           <t>narrateur|Ils font la dînette. Zoé sert un tout petit brocoli. Elle a goûté une petite portion, pour de vrai. Elle nomme le goût. Tom sert de l'eau.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5332,6 +5360,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5500,6 +5529,7 @@
 enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5667,6 +5697,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5834,6 +5865,7 @@
           <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6001,6 +6033,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6168,6 +6201,7 @@
           <t>enfant-f|Croquant. Elle a goûté une petite portion. Elle nomme le goût. Tom tapote.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6335,6 +6369,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6502,6 +6537,7 @@
           <t>narrateur|Léa a une assiette de betterave. Elle est rose. Zoé goûte une petite portion. C'est terreux et doux. Elle nomme le goût : c'est doux, maman. Léa ouvre les yeux.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6685,6 +6721,7 @@
           <t>narrateur|Zoé goûte la betterave. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6856,6 +6893,7 @@
           <t>narrateur|Les lèvres de Zoé sont un peu roses. Elle a goûté. Elle a nommé le goût. Une petite portion.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7051,6 +7089,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
 enfant-f|J'ai goûté une petite portion. J'ai nommé le goût.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>enfant-f|Doux et rose. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>enfant-f|Pas trop croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Dans le livre, une betterave. Léa montre. Zoé a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>enfant-f|Tendre, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|À la dînette, Léa sert du rose. Zoé a goûté une petite portion pour de vrai. Elle nomme le goût. Maman rit.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>enfant-f|Salé, un tout petit peu. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>enfant-f|Mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11311,6 +11374,7 @@
           <t>narrateur|Sami a des épinards. Ils sont verts et chauds. Zoé goûte une petite portion. C'est fondant. Elle nomme le goût : c'est doux, papa. Sami hoche.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11494,6 +11558,7 @@
           <t>narrateur|Zoé goûte les épinards. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11665,6 +11730,7 @@
           <t>narrateur|Zoé a goûté les épinards. Elle a nommé le goût. Une petite portion.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11860,6 +11926,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12028,6 +12095,7 @@
 enfant-f|J'ai goûté une petite portion. J'ai nommé le goût.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12223,6 +12291,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12390,6 +12459,7 @@
           <t>enfant-f|Doux. Elle a goûté une petite portion. Elle nomme le goût. Sami pose un cube.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12557,6 +12627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12724,6 +12795,7 @@
           <t>enfant-f|Un peu salé. Elle a goûté une petite portion. Elle nomme le goût. Maman range.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12891,6 +12963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13058,6 +13131,7 @@
           <t>enfant-f|Fondant, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13225,6 +13299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13392,6 +13467,7 @@
           <t>narrateur|Sami trouve les épinards dans le livre. Zoé a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13587,6 +13663,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13755,6 +13832,7 @@
 narrateur|Ils se taisent une seconde.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13922,6 +14000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14089,6 +14168,7 @@
           <t>enfant-f|Salé. Elle a goûté une petite portion. Elle nomme le goût. Sami ferme le livre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14256,6 +14336,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14423,6 +14504,7 @@
           <t>enfant-f|Pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14590,6 +14672,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14758,6 +14841,7 @@
 papa|Merci d'avoir dit le goût.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14953,6 +15037,7 @@
           <t>narrateur|On peut prendre doux, salé, ou croquant.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15121,6 +15206,7 @@
 narrateur|Un oiseau chante.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15288,6 +15374,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
 narrateur|La lumière est douce.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>enfant-f|Tout mou, pas croquant. Elle a goûté une petite portion. Elle nomme le goût.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
